--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_lstm_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_lstm_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>3.360186480545662</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>1.295281120905988</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,11 +987,11 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -998,7 +999,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1006,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,19 +1096,19 @@
         <v>2.235255047317524</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
@@ -1115,7 +1116,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,19 +1124,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>2.652685629804005</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,19 +1267,19 @@
         <v>0.1208088834528376</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1286,15 +1287,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
@@ -1302,15 +1303,15 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1393,19 +1394,19 @@
         <v>4.675349970958809</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
@@ -1413,7 +1414,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>4.074365359860171</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1564,19 +1565,19 @@
         <v>0.2449963326479303</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1584,15 +1585,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
@@ -1600,15 +1601,15 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1691,11 +1692,11 @@
         <v>4.579671457776772</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
@@ -1703,7 +1704,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,11 +1720,11 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
@@ -1731,7 +1732,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1739,7 +1740,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,27 +1833,27 @@
         <v>4.101478863958072</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,11 +1863,11 @@
         <v>0.2462473710392907</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
@@ -1874,7 +1875,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,15 +1883,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
@@ -1898,15 +1899,15 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196767172</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208222</v>
+        <v>0.08831268540851216</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997946</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798223</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278816</v>
+        <v>0.2724034021441992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668942</v>
+        <v>-0.08310591627222952</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.2302139203155766</v>
+        <v>0.06813883782630481</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.3570004269569067</v>
+        <v>0.01107374841991238</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4221174890977989</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1550900387558129</v>
+        <v>0.09453553638307291</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1953067267187089</v>
+        <v>0.302310379654222</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.968421052631579</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3976227638230778</v>
+        <v>-0.1729041606870662</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.137545638903235</v>
+        <v>-0.003824661998643064</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8451807666733799</v>
+        <v>1.018709317512736</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4221174890977989</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.042264956961712</v>
+        <v>0.2914329719196807</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1929195458612629</v>
+        <v>0.01495561057398431</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.463878208884358</v>
+        <v>1.069858047387411</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1348418208118199</v>
+        <v>-0.0675906456116333</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.3050913934539505</v>
+        <v>0.07488442474097812</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4395948126489193</v>
+        <v>0.01745895379357942</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1109469294357623</v>
+        <v>0.07812037677756986</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1530752451527519</v>
+        <v>0.2757884445827267</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2627477773058103</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.3922472502781837</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5584925916461387</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.770210184900723</v>
+        <v>0.2733293632849492</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.03400801284489896</v>
+        <v>0.0007277260805729213</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.081772824084672</v>
+        <v>1.003399227518678</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.06086540877310687</v>
+        <v>0.006315271644274922</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2239045209830171</v>
+        <v>0.02062259727917803</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1332122803819374</v>
+        <v>-0.01401823325590101</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3063348081442208</v>
+        <v>-0.123827674028805</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.4409663743242647</v>
+        <v>-0.1706369935164311</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.09553422240804788</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.02622046710983745</v>
+        <v>0.1153246048666685</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09148632702200347</v>
+        <v>0.2175075241759554</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.5817174515235457</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.05948551082612696</v>
+        <v>-0.1729041606870662</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.000761399900324</v>
+        <v>-0.003824661998643064</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.126441477249914</v>
+        <v>1.018709317512736</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.09452054742233507</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.232989781168045</v>
+        <v>0.05933591287199436</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2797909963696559</v>
+        <v>-0.1674527818089395</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3272379650361454</v>
+        <v>0.217823685038208</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.09553422240804788</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06187613924017166</v>
+        <v>-0.1797205616507378</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.7588405523925692</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3962635568098029</v>
+        <v>-0.1797205616507377</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.229548530008544</v>
+        <v>0.05578233354854656</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.3562664611678472</v>
+        <v>-0.0006226122544210622</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3517122056797888</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1234307695342148</v>
+        <v>0.09308385887610862</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1601694893969448</v>
+        <v>0.2888730135890062</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9667590027700831</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2919087280681923</v>
+        <v>-0.1729041606870662</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.337178913737862</v>
+        <v>-0.003824661998643064</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6204766553483896</v>
+        <v>1.018709317512736</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3517122056797888</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.73642661440255</v>
+        <v>0.2764933437769219</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.01427449029735994</v>
+        <v>0.003214343521740437</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.034323245798217</v>
+        <v>1.015014282496214</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.0005408736611124398</v>
+        <v>-0.01156825670987127</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.175494738854701</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.149754487788969</v>
+        <v>-0.01156825670987116</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.05788319793105123</v>
+        <v>-0.0177712977811868</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.03955356099954122</v>
+        <v>-0.02020589915817517</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.01908449673735646</v>
+        <v>0.00248480918072147</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,58 +2650,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.09426423307091425</v>
+        <v>-0.05011915684016077</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.000918619001137766</v>
+        <v>-0.1008663381248004</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.5457486744363677</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.3283373156263094</v>
+        <v>0.1116820459466649</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1742695681095055</v>
+        <v>0.2290143672035828</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9961218836565097</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4552117081539697</v>
+        <v>-0.1729041606870662</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.02879310222303655</v>
+        <v>-0.003824661998643064</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9675909316586796</v>
+        <v>1.018709317512736</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.517814916106651</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.6625463147527912</v>
+        <v>0.1484531755702008</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.02888017149412492</v>
+        <v>-0.09741425271664861</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9305571544596001</v>
+        <v>0.5449754826909824</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1348418208118203</v>
+        <v>-0.01394353365660617</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2637575043072632</v>
+        <v>-0.1107140668221784</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.09560278986700887</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1859301560821129</v>
+        <v>-0.1107140668221783</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2755,67 +2756,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.08580414120125246</v>
+        <v>0.06178134257150125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1977076985307631</v>
+        <v>0.00505590099202835</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4547922046947304</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2214144843240584</v>
+        <v>0.09312439303137932</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1850546701864588</v>
+        <v>0.2903937362392749</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9894736842105263</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4263473806405352</v>
+        <v>-0.1729041606870662</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08330128731178776</v>
+        <v>-0.003824661998643064</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9062373657240821</v>
+        <v>1.018709317512736</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4547922046947304</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.8927903483011224</v>
+        <v>0.2837464440076498</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1056090420633351</v>
+        <v>0.00891465854644502</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.253938671976573</v>
+        <v>1.041640602775754</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1348418208118202</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.1173859088485033</v>
+        <v>-0.005951937173018895</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.04768542881826432</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.07319060543591938</v>
+        <v>-0.005951937173018784</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1680244413169794</v>
+        <v>-0.01219022423981475</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.2219045237149262</v>
+        <v>-0.02020589915817517</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.06924610673126019</v>
+        <v>0.008180978954122731</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,67 +2864,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.478439838565154</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.6308086415152652</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1621362620897984</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06585467218022251</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1032868329403223</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8670360110803325</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.05454086493668719</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.7854308749751853</v>
+        <v>0.2117597153840092</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1159312148001902</v>
+        <v>-0.03587709265072067</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1621362620897984</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.563726853690139</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.08660219537318625</v>
+        <v>-0.2060850325577077</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.791763602304678</v>
+        <v>0.03737143334716839</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.09553422240804788</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.201774597206559</v>
+        <v>-0.04850246929027047</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.5695465868926448</v>
+        <v>0.2164120804427689</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2343173453769175</v>
+        <v>-0.2177835570628431</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.04751171863317727</v>
+        <v>0.1019572630080912</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.03788984189453015</v>
+        <v>-0.08312935668000898</v>
       </c>
     </row>
     <row r="10">
@@ -2973,73 +2974,73 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.2300350833857512</v>
+        <v>0.07488442474097812</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.3568031589971468</v>
+        <v>0.01745895379357942</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3873432105617136</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.136662982729604</v>
+        <v>0.07812037677756986</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1633505502872382</v>
+        <v>0.2757884445827267</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.968421052631579</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3316713576392679</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.2620900771361134</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7049954827482829</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3873432105617136</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.8404644143948521</v>
+        <v>0.2733293632849492</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.0750446292042426</v>
+        <v>0.0007277260805729213</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.180446040478912</v>
+        <v>1.003399227518678</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.0001453705952048079</v>
+        <v>0.006315271644274922</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1094852232504342</v>
+        <v>0.02062259727917803</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.09881212615383639</v>
+        <v>-0.01401823325590101</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.0575103862033457</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.09348711093957174</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.03968694231530989</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>0.04751171863317727</v>
+        <v>0.1019572630080912</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>-0.04657852252453465</v>
+        <v>-0.01914579833647312</v>
       </c>
     </row>
   </sheetData>
@@ -3283,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05390587101818811</v>
+        <v>-0.09123360655355661</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2215345333965962</v>
+        <v>0.2716992530341495</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389368129070568</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4707583434268612</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3313,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.122709994261599</v>
+        <v>0.7171104771509156</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3325,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756423</v>
+        <v>-0.1395291740668942</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3371,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.07923416091300595</v>
+        <v>0.236616904435895</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.1263300979645993</v>
+        <v>0.3607643431290386</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.3064991258757455</v>
+        <v>0.1551756964035938</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2922276320458878</v>
+        <v>0.1954076414005457</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9683860232945092</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.6131081926512691</v>
+        <v>-0.3950032996914198</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.2207471950377711</v>
+        <v>0.1431388531015461</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.217670160323774</v>
+        <v>0.8390787018579714</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.379905238616354</v>
+        <v>1.044006031446378</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1211636281216184</v>
+        <v>0.1903753769168413</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.229084309990409</v>
+        <v>1.455851036501685</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.2037181450170952</v>
+        <v>-0.1348418208118199</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3465,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2553938843122963</v>
+        <v>0.3109354176354568</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1911821718000761</v>
+        <v>0.442543900268815</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1742196764528615</v>
+        <v>0.1110081735734261</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118070551778035</v>
+        <v>0.1531549489989729</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9517470881863561</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.2609524087912378</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.3964274769943947</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.5543234919463098</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.306850557115716</v>
+        <v>0.7738173200609908</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.08674786633685749</v>
+        <v>0.03302457451902874</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.164014361496109</v>
+        <v>1.079076857355887</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.3634236100213168</v>
+        <v>0.0600982510694883</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.4066012997391519</v>
+        <v>0.2215729289627677</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03069646652952918</v>
+        <v>-0.1321858679615523</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3567,68 +3568,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.100164793498106</v>
+        <v>0.3117697537852107</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.04389284067202959</v>
+        <v>0.4434619977642447</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1902718302244096</v>
+        <v>-0.09553422240804799</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.05285602475691375</v>
+        <v>0.0262205355650471</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09098901137481945</v>
+        <v>0.09152169119601991</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3459302325581395</v>
+        <v>0.5812534664448142</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>0.06409273056642517</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499055</v>
+        <v>1.010598971850532</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389797</v>
+        <v>-0.1361478377629283</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.09452054742233496</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.07626111258301171</v>
+        <v>0.2327588715759248</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.4929777899512847</v>
+        <v>-0.2820736417488072</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.06792592296567937</v>
+        <v>0.3245788187347049</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1902718302244096</v>
+        <v>-0.09553422240804788</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.1948366748586146</v>
+        <v>0.06077294356864549</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>1.642107968541544</v>
+        <v>0.7588405523925696</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5477714426946109</v>
+        <v>-0.3968907857362824</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1251693621205769</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.09019523325487033</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3677,74 +3674,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1581174214000378</v>
+        <v>0.2374116069956718</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.09888126942605413</v>
+        <v>0.3616388281072549</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3517122056797887</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1773805784160715</v>
+        <v>0.1234988008759705</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2189630499919817</v>
+        <v>0.1602476670751302</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9680232558139535</v>
+        <v>0.9667221297836939</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.2888295617628096</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.3437537076012644</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.6135410360659561</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3517122056797887</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.128100074524097</v>
+        <v>0.7399649092036205</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.002539244775343397</v>
+        <v>0.01330982039701123</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.00480095509085</v>
+        <v>1.031870168936181</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1902718302244097</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.2577762686639147</v>
+        <v>0.0006426424844476752</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.4066012997391519</v>
+        <v>0.1754947388547012</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1058047018034436</v>
+        <v>-0.1487476639330719</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.07748680643409889</v>
+        <v>-0.05608499827733737</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.03772037593137512</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.07748680643409889</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1251693621205769</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.003372219793396858</v>
-      </c>
+        <v>-0.01908449673735646</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3789,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.1087528075876742</v>
+        <v>-0.08955008406229015</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.05204158936556458</v>
+        <v>0.00185253603501101</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.349301418079524</v>
+        <v>-0.5457486744363678</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1642843570386438</v>
+        <v>0.3284986481989144</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1461586070834201</v>
+        <v>0.1743586289563601</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9760174418604651</v>
+        <v>0.9961175818080976</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3171774434752518</v>
+        <v>-0.4528426721012546</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3752976474474206</v>
+        <v>0.03385158953966561</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.629933693721284</v>
+        <v>0.9619429552853161</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3438634194223723</v>
+        <v>-0.5178149161066509</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.6237788236386255</v>
+        <v>0.6639636709867729</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2350444346951552</v>
+        <v>-0.03095130270961111</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.5556010250437663</v>
+        <v>0.925887561460132</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1902718302244095</v>
+        <v>-0.1348418208118203</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.2041637086439727</v>
+        <v>-0.2637575043072633</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.7648927776578005</v>
+        <v>-0.09560278986700865</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3177128243212451</v>
+        <v>-0.1859301560821129</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3895,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.07482587463691437</v>
+        <v>0.09145550521126466</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01984997350713602</v>
+        <v>0.2010297839821997</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.510860276164316</v>
+        <v>-0.4547922046947305</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2294319934678644</v>
+        <v>0.2215369834589068</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2302205019383727</v>
+        <v>0.1851497650052599</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9811046511627907</v>
+        <v>0.9894620077648364</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.510860276164316</v>
+        <v>-0.4238528267792693</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.01480596234533527</v>
+        <v>0.0886277866925802</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.014599579382675</v>
+        <v>0.900361794320743</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.510860276164316</v>
+        <v>-0.4547922046947305</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.197380057805281</v>
+        <v>0.8944039924901468</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.03517676166105588</v>
+        <v>0.1032510823842867</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.066508772457122</v>
+        <v>1.247233196262338</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1902718302244097</v>
+        <v>-0.1348418208118202</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1673172798229374</v>
+        <v>-0.1173859088485033</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.2642803867769432</v>
+        <v>-0.0476854288182641</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.07669430607967864</v>
+        <v>-0.07319060543591949</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1438337496556286</v>
+        <v>-0.1674223683879634</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.1011807062801673</v>
+        <v>-0.2204193883124588</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.04745452581345688</v>
+        <v>0.06798144942288076</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -4003,64 +3996,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.03221500196355853</v>
+        <v>0.4793639545490427</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.02058141021045246</v>
+        <v>0.6278814503017012</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2662983461899697</v>
+        <v>-0.1621362620897984</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1551500673867337</v>
+        <v>0.06589116382333747</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1311004930543385</v>
+        <v>0.1033433615741785</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9905523255813954</v>
+        <v>0.8674431503050472</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2173700304676902</v>
+        <v>-0.05475573564807934</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.5763233736708298</v>
+        <v>0.7860352687889605</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.431710101123582</v>
+        <v>0.1163138931314266</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2256684877367606</v>
+        <v>-0.1621362620897984</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3189055392044311</v>
+        <v>0.5650599642234546</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3786689925755862</v>
+        <v>-0.08855022140436064</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2840497909829098</v>
+        <v>0.7879677988647459</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1902718302244096</v>
+        <v>-0.09553422240804788</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1210396369472986</v>
+        <v>0.1962993140740552</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>1.022865190388677</v>
+        <v>0.5623957351664832</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.4458159435073871</v>
+        <v>-0.2343173453769176</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.04297628997207603</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.03348640752128329</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4109,70 +4106,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1146983328320856</v>
+        <v>0.2340816694952572</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.05768300897229595</v>
+        <v>0.3579745888435362</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.5038538797878841</v>
+        <v>-0.3873432105617136</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.2251206364429028</v>
+        <v>0.1367385298855959</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2259952594952164</v>
+        <v>0.1634379966126062</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9745639534883721</v>
+        <v>0.9683860232945092</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.5038538797878841</v>
+        <v>-0.3300438329401948</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.0006941255855289485</v>
+        <v>0.2658795065335533</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.000684450044591</v>
+        <v>0.7010897152404303</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.5038538797878841</v>
+        <v>-0.3873432105617136</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>1.246713795434945</v>
+        <v>0.8420334496078963</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.05841768376677448</v>
+        <v>0.07275185500251391</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.110450429591929</v>
+        <v>1.174203245437579</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1902718302244099</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.2106208609317974</v>
+        <v>-0.002050137703555222</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.282389832992527</v>
+        <v>0.1073716050320477</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.05596501953953625</v>
+        <v>-0.09881212615383639</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1120728348595418</v>
+        <v>-0.05862512150203503</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.0883060941075906</v>
+        <v>-0.09348711093957196</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.02606877220341508</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0.03845724628766156</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.04297628997207603</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.04475874586109485</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4415,28 +4416,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093203</v>
+        <v>0.05390587101818811</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.0812675747870259</v>
+        <v>0.2215345333965962</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962869</v>
+        <v>0.2389368129070568</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4445,10 +4446,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165606</v>
+        <v>1.122709994261599</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4457,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756423</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4503,49 +4504,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.05461060122071615</v>
+        <v>-0.07923416091300595</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.03048703307917489</v>
+        <v>-0.1263300979645993</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.04772879566569357</v>
+        <v>0.3064991258757455</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1794422862086121</v>
+        <v>0.2922276320458878</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6131081926512691</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.0421307841692844</v>
+        <v>-0.2207471950377711</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8265584394738612</v>
+        <v>1.217670160323774</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2577947586899569</v>
+        <v>1.379905238616354</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.01117302287485056</v>
+        <v>0.1211636281216184</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9477507323406914</v>
+        <v>1.229084309990409</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.0232535172924333</v>
+        <v>-0.2037181450170952</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4597,58 +4598,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.2553938843122963</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>0.1911821718000761</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.1742196764528615</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.2118070551778035</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>1.306850557115716</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>0.08674786633685749</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>1.164014361496109</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03380094055205907</v>
+        <v>0.3634236100213168</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02261670626072965</v>
+        <v>0.4066012997391519</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.05516988571317594</v>
+        <v>-0.03069646652952918</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4699,64 +4700,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.05461060122071615</v>
+        <v>0.100164793498106</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03048703307917489</v>
+        <v>0.04389284067202959</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.1902718302244096</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04772879566569357</v>
+        <v>0.05285602475691375</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1794422862086121</v>
+        <v>0.09098901137481945</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.3459302325581395</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.0421307841692844</v>
+        <v>1.058870045499055</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8265584394738612</v>
+        <v>-0.04411026616389797</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2577947586899569</v>
+        <v>0.07626111258301171</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01117302287485056</v>
+        <v>-0.4929777899512847</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9477507323406914</v>
+        <v>0.06792592296567937</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0232535172924333</v>
+        <v>-0.1902718302244096</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>0.1948366748586146</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>1.642107968541544</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.5477714426946109</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1251693621205769</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.09019523325487033</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4805,70 +4810,74 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.05461060122071615</v>
+        <v>0.1581174214000378</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03048703307917489</v>
+        <v>0.09888126942605413</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04772879566569357</v>
+        <v>0.1773805784160715</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1794422862086121</v>
+        <v>0.2189630499919817</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.9680232558139535</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.0421307841692844</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8265584394738612</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2577947586899569</v>
+        <v>1.128100074524097</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01117302287485056</v>
+        <v>0.002539244775343397</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9477507323406914</v>
+        <v>1.00480095509085</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0232535172924333</v>
+        <v>-0.1902718302244097</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>0.2577762686639147</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.4066012997391519</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1058047018034436</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.03498341280871453</v>
+        <v>-0.07748680643409889</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.02211650379097496</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.05839132864093699</v>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+        <v>-0.07748680643409889</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1251693621205769</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.003372219793396858</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4913,58 +4922,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.02663369733678067</v>
+        <v>0.1087528075876742</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.003150083645206303</v>
+        <v>0.05204158936556458</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.06736333266626204</v>
+        <v>-0.349301418079524</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.02836892359066607</v>
+        <v>0.1642843570386438</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.09489875555234854</v>
+        <v>0.1461586070834201</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.9760174418604651</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.03083597722305176</v>
+        <v>-0.3171774434752518</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2045841847288317</v>
+        <v>0.3752976474474206</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1577797337984095</v>
+        <v>0.629933693721284</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.06736333266626204</v>
+        <v>-0.3438634194223723</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.05929819226591238</v>
+        <v>0.6237788236386255</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1672229335544289</v>
+        <v>-0.2350444346951552</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2180025126658519</v>
+        <v>0.5556010250437663</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02263489326825618</v>
+        <v>-0.1902718302244095</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.02652818381642674</v>
+        <v>0.2041637086439727</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1558858091780142</v>
+        <v>0.7648927776578005</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1578131607344163</v>
+        <v>-0.3177128243212451</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5019,67 +5028,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.02318343280290613</v>
+        <v>0.07482587463691437</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.0002212582119068829</v>
+        <v>0.01984997350713602</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1494667234990011</v>
+        <v>-0.510860276164316</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04881367825974163</v>
+        <v>0.2294319934678644</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1684565663672502</v>
+        <v>0.2302205019383727</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.9811046511627907</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1494667234990011</v>
+        <v>-0.510860276164316</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.05713677910069714</v>
+        <v>-0.01480596234533527</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.764782632793077</v>
+        <v>1.014599579382675</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1494667234990011</v>
+        <v>-0.510860276164316</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2029904779412877</v>
+        <v>1.197380057805281</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.05425791481911957</v>
+        <v>0.03517676166105588</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7462695328046527</v>
+        <v>1.066508772457122</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1902718302244097</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.02979978428192642</v>
+        <v>0.1673172798229374</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.0143993394681019</v>
+        <v>0.2642803867769432</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.04357171976591001</v>
+        <v>-0.07669430607967864</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.004141130371642987</v>
+        <v>-0.1438337496556286</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.008035627368806919</v>
+        <v>-0.1011807062801673</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.01227539826672475</v>
+        <v>-0.04745452581345688</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5127,58 +5136,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.05181498386144323</v>
+        <v>0.03221500196355853</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.02775536374563381</v>
+        <v>-0.02058141021045246</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.06736333266626204</v>
+        <v>-0.2662983461899697</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.02684214139493521</v>
+        <v>0.1551500673867337</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1013502638837152</v>
+        <v>0.1311004930543385</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8758620689655172</v>
+        <v>0.9905523255813954</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03083597722305176</v>
+        <v>-0.2173700304676902</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2045841847288317</v>
+        <v>0.5763233736708298</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1577797337984095</v>
+        <v>0.431710101123582</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.06736333266626204</v>
+        <v>-0.2256684877367606</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08528067400570105</v>
+        <v>0.3189055392044311</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1467965653417611</v>
+        <v>-0.3786689925755862</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3135239120226523</v>
+        <v>0.2840497909829098</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.02263489326825641</v>
+        <v>-0.1902718302244096</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.002650852699600192</v>
+        <v>0.1210396369472986</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1558858091780142</v>
+        <v>1.022865190388677</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1371559894747344</v>
+        <v>-0.4458159435073871</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5233,67 +5242,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.03304622263546775</v>
+        <v>0.1146983328320856</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.009415926376106443</v>
+        <v>0.05768300897229595</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1494667234990011</v>
+        <v>-0.5038538797878841</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.04808556290438997</v>
+        <v>0.2251206364429028</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1694529954673782</v>
+        <v>0.2259952594952164</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9103448275862069</v>
+        <v>0.9745639534883721</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1494667234990011</v>
+        <v>-0.5038538797878841</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.05713677910069714</v>
+        <v>-0.0006941255855289485</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.764782632793077</v>
+        <v>1.000684450044591</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1494667234990011</v>
+        <v>-0.5038538797878841</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.2145864849466057</v>
+        <v>1.246713795434945</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04514160671354794</v>
+        <v>0.05841768376677448</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7889008267354013</v>
+        <v>1.110450429591929</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1902718302244099</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.02044771649392441</v>
+        <v>0.2106208609317974</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.0143993394681019</v>
+        <v>0.282389832992527</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03435240403478412</v>
+        <v>-0.05596501953953625</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.01382036540768761</v>
+        <v>-0.1120728348595418</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.008035627368806919</v>
+        <v>-0.0883060941075906</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02203304209255141</v>
+        <v>-0.02606877220341508</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5539,28 +5548,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714601</v>
+        <v>0.01891210187562598</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.08099293800752018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886583</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348786</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5569,10 +5578,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473792</v>
+        <v>0.2720069211165606</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5581,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886086</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5627,49 +5636,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.00261610496364173</v>
+        <v>0.05267606622749588</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.09149221629784987</v>
+        <v>0.03313726894568902</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1344899709337924</v>
+        <v>0.04874012228299625</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4858267016059757</v>
+        <v>0.1788458642458411</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.04302517385398152</v>
+        <v>0.04481096576608823</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.105225225534033</v>
+        <v>0.8195994866558804</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.468377917107822</v>
+        <v>0.2577947586899569</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.05064609968796929</v>
+        <v>-0.01117302287485056</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8567164293695581</v>
+        <v>0.9477507323406914</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.09945162290284171</v>
+        <v>-0.0232535172924333</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5721,58 +5730,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.0009544101684616502</v>
+        <v>0.01970412365980478</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08997859384708495</v>
+        <v>0.0007773210100467942</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1202708276706985</v>
+        <v>0.04505087866076889</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.428252010780779</v>
+        <v>0.1645456863596117</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.07118238373413943</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7134331218450367</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4189993189650008</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08257096330288938</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7663973627717755</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.001666053365659614</v>
+        <v>-0.03132202167933151</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03652221211175721</v>
+        <v>0.02524037250002897</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03362799015670248</v>
+        <v>-0.05516988571317594</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5823,58 +5832,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.2559246807074843</v>
+        <v>0.05267606622749588</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.3222286597947619</v>
+        <v>0.03313726894568902</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2428303606266991</v>
+        <v>0.04874012228299625</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4115841927752237</v>
+        <v>0.1788458642458411</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04302517385398152</v>
+        <v>0.04481096576608823</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.105225225534033</v>
+        <v>0.8195994866558804</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.09544957859406078</v>
+        <v>0.2577947586899569</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.291756353785401</v>
+        <v>-0.01117302287485056</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1745881246128611</v>
+        <v>0.9477507323406914</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0560149404613729</v>
+        <v>-0.0232535172924333</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2539729957586778</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2539729957586779</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5929,67 +5938,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.03813420729598083</v>
+        <v>0.05267606622749588</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1238453278648692</v>
+        <v>0.03313726894568902</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1485663937076736</v>
+        <v>0.04874012228299625</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4598254464999732</v>
+        <v>0.1788458642458411</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.04302517385398152</v>
+        <v>0.04481096576608823</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.105225225534033</v>
+        <v>0.8195994866558804</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4160871217762194</v>
+        <v>0.2577947586899569</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08445379314351564</v>
+        <v>-0.01117302287485056</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7610706232179582</v>
+        <v>0.9477507323406914</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.0232535172924333</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.03561126513983293</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.03561126513983315</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.03721531580334436</v>
+        <v>0.03233481340582589</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.03523533956628744</v>
+        <v>-0.02461898026750631</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.002052289349162906</v>
+        <v>0.05839132864093699</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -6037,68 +6046,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0375586808667554</v>
+        <v>0.02475048204345986</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05489737471566047</v>
+        <v>0.005730013567496695</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.09945162290284193</v>
+        <v>-0.06907412361301446</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04136068042703184</v>
+        <v>0.02981856460838314</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1458435240007064</v>
+        <v>0.09460808229514034</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4180327868852459</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.0007182735616988456</v>
+        <v>-0.03261377247189712</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4098984628208118</v>
+        <v>0.2076821686025976</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.002474931135736743</v>
+        <v>0.1639106815081905</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.06907412361301446</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.03681396480743415</v>
+        <v>0.05929819226591238</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.3296661779505354</v>
+        <v>-0.1672229335544289</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.06733692458327654</v>
+        <v>0.2180025126658519</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09945162290284182</v>
+        <v>-0.02263489326825618</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.04028016296466519</v>
+        <v>-0.02652818381642674</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4732868872829521</v>
+        <v>0.1558858091780142</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2939052319381199</v>
+        <v>-0.1578131607344163</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.03162272672093414</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.03005298610629403</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6147,74 +6152,70 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.005253986618082518</v>
+        <v>0.02130654653516961</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.08432342252042024</v>
+        <v>0.002350001197488849</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1510269073093905</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1205050988973878</v>
+        <v>0.04999892582241082</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4378794843170654</v>
+        <v>0.167895117651285</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1510269073093905</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.05985555354214966</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7590328081330525</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1510269073093905</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4278174458869728</v>
+        <v>0.2029904779412877</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.07686975853177058</v>
+        <v>-0.05425791481911957</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7825267188630456</v>
+        <v>0.7462695328046527</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09945162290284171</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.007890734571603719</v>
+        <v>-0.02979978428192642</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03652221211175721</v>
+        <v>0.0143993394681019</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02762263770674156</v>
+        <v>-0.04357171976591001</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.006214327804190622</v>
+        <v>0.001571458659609615</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0</v>
+        <v>-0.0105741378536347</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.006214327804190845</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.03162272672093414</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.01099744741745334</v>
-      </c>
+        <v>0.01227539826672475</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6259,58 +6260,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.04833213783822321</v>
+        <v>0.04988557703553198</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1331345286644704</v>
+        <v>0.03039857422724657</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1356398011824084</v>
+        <v>-0.06907412361301446</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.09298519050858571</v>
+        <v>0.02814038298213805</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1269236686122974</v>
+        <v>0.1010409405890451</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.8835616438356164</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.09531272857105433</v>
+        <v>-0.03261377247189712</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2746016806323299</v>
+        <v>0.2076821686025976</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.3284158740502707</v>
+        <v>0.1639106815081905</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1356398011824084</v>
+        <v>-0.06907412361301446</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.05193019976795488</v>
+        <v>0.08528067400570105</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3198930422675438</v>
+        <v>-0.1467965653417611</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.09498623589337274</v>
+        <v>0.3135239120226523</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0009963797895713444</v>
+        <v>-0.02263489326825641</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.04583594451654438</v>
+        <v>-0.002650852699600414</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3319072203450488</v>
+        <v>0.1558858091780142</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2836107193440499</v>
+        <v>-0.1371559894747344</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6365,67 +6366,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.012087515578599</v>
+        <v>0.03115124446533635</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.1001196368017815</v>
+        <v>0.01201197097098006</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3118935599689732</v>
+        <v>-0.1510269073093905</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.137264618687214</v>
+        <v>0.04920088103301951</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4303399232469794</v>
+        <v>0.1688893553335784</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.910958904109589</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3118935599689732</v>
+        <v>-0.1510269073093905</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.03053612821128215</v>
+        <v>0.05985555354214966</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.07468118522596</v>
+        <v>0.7590328081330525</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3118935599689732</v>
+        <v>-0.1510269073093905</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4356971929762141</v>
+        <v>0.2145864849466057</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.07177524672695001</v>
+        <v>-0.04514160671354794</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7969396716177674</v>
+        <v>0.7889008267354013</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.009496253811690059</v>
+        <v>-0.02044771649392452</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.01305054772756753</v>
+        <v>0.0143993394681019</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.02225634405887633</v>
+        <v>-0.03435240403478412</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.01114374110996741</v>
+        <v>0.01122592381449516</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.02264463231942671</v>
+        <v>-0.0105741378536347</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.01176735872106871</v>
+        <v>0.02203304209255141</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6671,28 +6672,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363066</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752891</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.4518304992174232</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450097</v>
+        <v>-0.2902196151348786</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6701,10 +6702,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682992</v>
+        <v>0.5657770181230022</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6713,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.05185156587886086</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6759,49 +6760,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.171220671088737</v>
+        <v>-0.01373903328845372</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1038660379375795</v>
+        <v>-0.1125621705165718</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3380397400935387</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1740509194643686</v>
+        <v>0.1323679496907128</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2513047692917923</v>
+        <v>0.4781070119682687</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9317738791423001</v>
+        <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3340616179283677</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.03510779298083788</v>
+        <v>-0.04302517385398152</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.078204809253966</v>
+        <v>1.105225225534033</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3340616179283675</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7587523149593043</v>
+        <v>0.4520024147490922</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1440304211262609</v>
+        <v>-0.07266334992596768</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.41207876134175</v>
+        <v>0.7989055763499129</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1136737333480079</v>
+        <v>-0.09945162290284171</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6853,58 +6854,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.05550959933794908</v>
+        <v>0.001402698831345583</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.005190714109256422</v>
+        <v>-0.09893763670599443</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1161134555088488</v>
+        <v>0.1183626651723915</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1734081721485486</v>
+        <v>0.4213989939818436</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9727095516569201</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2377598766809244</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1044258367867865</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7673849036436503</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3847468363930642</v>
+        <v>0.4223472503301919</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09925207039248651</v>
+        <v>-0.09160293332491798</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7160345022383415</v>
+        <v>0.7464906434894674</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07769789874505417</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.0987952779583593</v>
+        <v>0.01535266286598147</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1446105883668447</v>
+        <v>0.03652221211175721</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2126538656893789</v>
+        <v>-0.02042363298963568</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6955,68 +6956,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.004956784885090215</v>
+        <v>-0.2559124096816751</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.06217979364680559</v>
+        <v>-0.3304698265618605</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2964510710497926</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1791172556944993</v>
+        <v>0.2432532731854319</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2096064137750668</v>
+        <v>0.4050020947351894</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9610136452241715</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2894994192055534</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.0294593192818966</v>
+        <v>-0.04302517385398152</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9343775199298385</v>
+        <v>1.105225225534033</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2949492194044457</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.400481916569726</v>
+        <v>0.09546764435931765</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.08901674035320328</v>
+        <v>-0.3003680398422724</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7453183305541279</v>
+        <v>0.1687372256229796</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1006434165352605</v>
+        <v>-0.0560149404613729</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1504220855409401</v>
+        <v>-0.2455469541704476</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.06691639935843341</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2037071367822867</v>
+        <v>-0.2455469541704476</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.9369318333737771</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.4830240439158506</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7065,74 +7062,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03940481683370378</v>
+        <v>-0.03586481885198423</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.02036934175274074</v>
+        <v>-0.1324709571144885</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3222855056082222</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1835940033086571</v>
+        <v>0.1463734099386641</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.227877584968094</v>
+        <v>0.4524634263126237</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9824561403508771</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3208388022069446</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.01594897560683151</v>
+        <v>-0.04302517385398152</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.035527342769999</v>
+        <v>1.105225225534033</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3208388022069444</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5304243237264812</v>
+        <v>0.4194281822175281</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.004492009089300142</v>
+        <v>-0.09346722694966614</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9871481210220722</v>
+        <v>0.7413312467321582</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1006434165352603</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1125457033920862</v>
+        <v>-0.02243400713434263</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.01985591471734827</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1298238468775555</v>
+        <v>-0.02243400713434285</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.01525782665960285</v>
+        <v>-0.03721531580334425</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1089931151410186</v>
+        <v>-0.03523533956628744</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1052015310703811</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.9369318333737771</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.1364142214693028</v>
-      </c>
+        <v>-0.002052289349162906</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7177,67 +7170,67 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3963424998129652</v>
+        <v>0.02598771917637577</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3160415461584793</v>
+        <v>-0.07681603012397031</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1301899711886676</v>
+        <v>-0.09945162290284193</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04696331126810462</v>
+        <v>0.04114367315616457</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1233071203275871</v>
+        <v>0.1439311565984641</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8810916179337231</v>
+        <v>0.4365079365079365</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.05375906249190954</v>
+        <v>0.0007182735616988456</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3710285082589708</v>
+        <v>0.4098984628208118</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1735107435544729</v>
+        <v>-0.002474931135736743</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1301899711886676</v>
+        <v>0</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4756733137019094</v>
+        <v>0.02525130826755007</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.04010635940044582</v>
+        <v>-0.3452124431506953</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.8852535542531341</v>
+        <v>0.04463120179628846</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1006434165352604</v>
+        <v>-0.09945162290284182</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1922112837326895</v>
+        <v>0.04028016296466541</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4209136505459858</v>
+        <v>0.4732868872829521</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1609544441531808</v>
+        <v>-0.2939052319381199</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="n">
-        <v>0.06240731361029761</v>
+        <v>0.03162272672093414</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.05963501310249986</v>
+        <v>-0.03005298610629403</v>
       </c>
     </row>
     <row r="8">
@@ -7287,73 +7280,73 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2315403584866602</v>
+        <v>-0.005956709781799518</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1607168569004001</v>
+        <v>-0.1055596341553178</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2536022225426302</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1243562028680092</v>
+        <v>0.1186004946818295</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1977786680991317</v>
+        <v>0.4309492518391503</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9161793372319688</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2536022225426301</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08147152678694947</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8185170678350435</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2536022225426302</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.649978598116872</v>
+        <v>0.4118942780971639</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.07327546602071733</v>
+        <v>-0.09827883424314621</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.209645039141326</v>
+        <v>0.7280152160716017</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1006434165352603</v>
+        <v>-0.09945162290284171</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05150155635645648</v>
+        <v>0.007890734571603719</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1208210812769805</v>
+        <v>0.03652221211175721</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.06184709234907204</v>
+        <v>-0.02762263770674167</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.16677324323637</v>
+        <v>-0.007349100039108825</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.02078393064999295</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1915380882289455</v>
+        <v>-0.007349100039108825</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>0.06240731361029761</v>
+        <v>0.03162272672093414</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.0004441817764544442</v>
+        <v>-0.01099744741745334</v>
       </c>
     </row>
     <row r="9">
@@ -7399,68 +7392,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3994460475529011</v>
+        <v>-0.05894523623747761</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.3189666148767838</v>
+        <v>-0.1532387216306568</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1089126807529314</v>
+        <v>-0.1356398011824084</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.05049802574037217</v>
+        <v>0.09203834272922401</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1204080049813822</v>
+        <v>0.1252604052872642</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.6140350877192983</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03238849291247448</v>
+        <v>-0.09531272857105433</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4019927785306603</v>
+        <v>0.2746016806323299</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1045358908313918</v>
+        <v>0.3284158740502707</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1017127797251618</v>
+        <v>-0.1356398011824084</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4462891742215649</v>
+        <v>0.04019896541280454</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.05922010792444365</v>
+        <v>-0.3356659643275656</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.8305680943705854</v>
+        <v>0.07105089836658075</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1006434165352604</v>
+        <v>-0.01115210339786621</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1948611240373785</v>
+        <v>-0.04583594451654438</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4530045618896967</v>
+        <v>0.3319072203450488</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1776618220087287</v>
+        <v>-0.28361071934405</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.06240731361029761</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.05869370908356775</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7509,74 +7498,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.2659527306001281</v>
+        <v>-0.0231048177529094</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.1931502401206739</v>
+        <v>-0.1209895053874418</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2411007355370326</v>
+        <v>-0.3118935599689732</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1116812781801663</v>
+        <v>0.1351307371672041</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1953141980997989</v>
+        <v>0.4235263327127929</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9103313840155945</v>
+        <v>1</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.2411007355370325</v>
+        <v>-0.3118935599689732</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.099585195727802</v>
+        <v>-0.03053612821128215</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7781677349908507</v>
+        <v>1.07468118522596</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2411007355370326</v>
+        <v>-0.3118935599689732</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.6681433095023164</v>
+        <v>0.4196861494321171</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.08509121872174941</v>
+        <v>-0.09330247346842124</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.243450541474013</v>
+        <v>0.7417871988233988</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1006434165352603</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.08088318610644962</v>
+        <v>-0.009496253811690059</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1395938196296003</v>
+        <v>0.01305054772756753</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.05151891183670421</v>
+        <v>-0.02225634405887633</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.1993758573054911</v>
+        <v>-0.02447318807194721</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.004382948042095713</v>
+        <v>-0.02264463231942671</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.204655801090279</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.06240731361029761</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.0008976402154885488</v>
-      </c>
+        <v>-0.001870922095470795</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7819,28 +7804,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003975565</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252798</v>
+        <v>0.1799741913752891</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213004998</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450097</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7849,10 +7834,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922789</v>
+        <v>0.5373300241682992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7861,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7907,49 +7892,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.01216599018987663</v>
+        <v>0.171220671088737</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.009793428505060708</v>
+        <v>0.1038660379375795</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1711634614757399</v>
+        <v>-0.3380397400935387</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.0826181758453077</v>
+        <v>0.1740509194643686</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2821735006319364</v>
+        <v>0.2513047692917923</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9317738791423001</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1711634614757399</v>
+        <v>-0.3340616179283677</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06836536404139437</v>
+        <v>-0.03510779298083788</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.763436773988745</v>
+        <v>1.078204809253966</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1711634614757399</v>
+        <v>-0.3340616179283675</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1918321211670491</v>
+        <v>0.7587523149593043</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.07315736280592</v>
+        <v>0.1440304211262609</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.6709631884831277</v>
+        <v>1.41207876134175</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07691029042613784</v>
+        <v>-0.1136737333480079</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -8001,58 +7986,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>0.05550959933794908</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.005190714109256422</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.1161134555088488</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.1734081721485486</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9727095516569201</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809244</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>0.1044258367867865</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>0.7673849036436503</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.3847468363930642</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.09925207039248651</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.7160345022383415</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.07769789874505417</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03770392438138437</v>
+        <v>-0.0987952779583593</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02388919002588441</v>
+        <v>0.1446105883668447</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.06015603544531201</v>
+        <v>-0.2126538656893789</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8103,67 +8088,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.004956784885090215</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252243</v>
+        <v>-0.06217979364680559</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2964510710497926</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.1791172556944993</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2096064137750668</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.9610136452241715</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2894994192055534</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2963414873615395</v>
+        <v>0.0294593192818966</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884719</v>
+        <v>0.9343775199298385</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2949492194044457</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.400481916569726</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452529</v>
+        <v>-0.08901674035320328</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010954</v>
+        <v>0.7453183305541279</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1006434165352605</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.02739595200487099</v>
+        <v>-0.1504220855409401</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2133877894148128</v>
+        <v>0.06691639935843341</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1532830963295269</v>
+        <v>-0.2037071367822867</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1633577678331091</v>
+        <v>0.9369318333737771</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1230760609717061</v>
+        <v>-0.4830240439158506</v>
       </c>
     </row>
     <row r="6">
@@ -8213,73 +8198,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>0.03940481683370378</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.02036934175274074</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3222855056082222</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.1835940033086571</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.227877584968094</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9824561403508771</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3208388022069446</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>-0.01594897560683151</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>1.035527342769999</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3208388022069444</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.5304243237264812</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.004492009089300142</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.9871481210220722</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.1006434165352603</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.03770392438138437</v>
+        <v>-0.1125457033920862</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.02388919002588441</v>
+        <v>0.01985591471734827</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.06015603544531201</v>
+        <v>-0.1298238468775555</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0</v>
+        <v>-0.01525782665960285</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1089931151410186</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>0.1052015310703811</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1633577678331091</v>
+        <v>0.9369318333737771</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.03616593443698046</v>
+        <v>-0.1364142214693028</v>
       </c>
     </row>
     <row r="7">
@@ -8325,64 +8310,68 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0592751493456467</v>
+        <v>0.3963424998129652</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.06181929705473221</v>
+        <v>0.3160415461584793</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04166741338965119</v>
+        <v>-0.1301899711886676</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.02723991449737863</v>
+        <v>0.04696331126810462</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1218498136071539</v>
+        <v>0.1233071203275871</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.875</v>
+        <v>0.8810916179337231</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.0337965427970921</v>
+        <v>-0.05375906249190954</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2454305044642098</v>
+        <v>0.3710285082589708</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1507420063986119</v>
+        <v>0.1735107435544729</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.04166741338965119</v>
+        <v>-0.1301899711886676</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.09632721912647146</v>
+        <v>0.4756733137019094</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1474279028426946</v>
+        <v>-0.04010635940044582</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3369196862840718</v>
+        <v>0.8852535542531341</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02816541798993888</v>
+        <v>-0.1006434165352604</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.07232099606416198</v>
+        <v>0.1922112837326895</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1657346319736688</v>
+        <v>0.4209136505459858</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.08013284786036701</v>
+        <v>-0.1609544441531808</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.06240731361029761</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.05963501310249986</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8431,70 +8420,74 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.0001303437097192051</v>
+        <v>0.2315403584866602</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.002271124971016336</v>
+        <v>0.1607168569004001</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1581669849073072</v>
+        <v>-0.2536022225426302</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07377310901784989</v>
+        <v>0.1243562028680092</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2435438105867264</v>
+        <v>0.1977786680991317</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9161793372319688</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1581669849073072</v>
+        <v>-0.2536022225426301</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08511774496925661</v>
+        <v>0.08147152678694947</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7054688639039697</v>
+        <v>0.8185170678350435</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1581669849073072</v>
+        <v>-0.2536022225426302</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1877292032555731</v>
+        <v>0.649978598116872</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.07634804645148208</v>
+        <v>0.07327546602071733</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6566125840732896</v>
+        <v>1.209645039141326</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.1006434165352603</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.01218387538860988</v>
+        <v>0.05150155635645648</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.01568038565429664</v>
+        <v>0.1208210812769805</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.003442530066615768</v>
+        <v>-0.06184709234907204</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.05184246411679871</v>
+        <v>0.16677324323637</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.008017278091763336</v>
+        <v>-0.02078393064999295</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.06034353309441953</v>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+        <v>0.1915380882289455</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.06240731361029761</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.0004441817764544442</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8539,64 +8532,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.03267126890886141</v>
+        <v>0.3994460475529011</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.03034795642800281</v>
+        <v>0.3189666148767838</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1113481108072819</v>
+        <v>-0.1089126807529314</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.07210104096467018</v>
+        <v>0.05049802574037217</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1382962075459775</v>
+        <v>0.1204080049813822</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.6140350877192983</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.08046307630867644</v>
+        <v>-0.03238849291247448</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1852776205766054</v>
+        <v>0.4019927785306603</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.3588877606977632</v>
+        <v>0.1045358908313918</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1113481108072819</v>
+        <v>-0.1017127797251618</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.05197377741827158</v>
+        <v>0.4462891742215649</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.181919892235637</v>
+        <v>-0.05922010792444365</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.181786507921208</v>
+        <v>0.8305680943705854</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01716678696259688</v>
+        <v>-0.1006434165352604</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.02075781813072641</v>
+        <v>0.1948611240373785</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1094309685339827</v>
+        <v>0.4530045618896967</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1173473522527883</v>
+        <v>-0.1776618220087287</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.06240731361029761</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.05869370908356775</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8645,70 +8642,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.02216239784404961</v>
+        <v>0.2659527306001281</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.01981384534858188</v>
+        <v>0.1931502401206739</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1612117183471059</v>
+        <v>-0.2411007355370326</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.08024329625802588</v>
+        <v>0.1116812781801663</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2449253111481129</v>
+        <v>0.1953141980997989</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9103313840155945</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1612117183471059</v>
+        <v>-0.2411007355370325</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.08119310169084692</v>
+        <v>0.099585195727802</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7190492241917</v>
+        <v>0.7781677349908507</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1612117183471059</v>
+        <v>-0.2411007355370326</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1657740380314439</v>
+        <v>0.6681433095023164</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.09342174573761797</v>
+        <v>0.08509121872174941</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.5798209207541541</v>
+        <v>1.243450541474013</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.1006434165352603</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.01011952165535834</v>
+        <v>0.08088318610644962</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.01200688273993444</v>
+        <v>0.1395938196296003</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.02186388726466693</v>
+        <v>-0.05151891183670421</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.02866519299509074</v>
+        <v>0.1993758573054911</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.01160507152697798</v>
+        <v>-0.004382948042095713</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.04074309100744022</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0.204655801090279</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.06240731361029761</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0.0008976402154885488</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8721,7 +8722,1139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651871976</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947869</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.006399259684120362</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.01126878037121148</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1711634614757399</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.08216067292169081</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.2807448381846609</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1711634614757399</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.06836536404139437</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.763436773988745</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1711634614757399</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.1987897421667504</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.07453830598866218</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.6730823740164141</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.07691029042613784</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.04521242326464603</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.04989172518949392</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.07269182521527755</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2314419517208828</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.09388774724005255</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6751222101795875</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1250839088436306</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1314389641828525</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.4235217239987224</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>-0.03906313874946032</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.02388919002588441</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.06148353687936992</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.0100920662696089</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.2963414873615395</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884719</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.0216043007611717</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.2133877894148128</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1580562210421895</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1633577678331091</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.1230760609717061</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.04521242326464603</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.04989172518949392</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.07269182521527755</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2314419517208828</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.09388774724005255</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6751222101795875</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1250839088436306</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1314389641828525</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.4235217239987224</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>-0.03906313874946032</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.02388919002588441</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.06148353687936992</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1633577678331091</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.03616593443698046</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.06545893554561277</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.06023724627207616</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.04166741338965119</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.02708815891828022</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.1214670058598442</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.8651685393258427</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.0337965427970921</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.2454305044642098</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.1507420063986119</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.04166741338965119</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.1027273061411338</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1486981871154701</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.3478244819885395</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.02816541798993888</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.07232099606416198</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.1657346319736688</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.08013284786036678</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.005706647921918995</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.0007777976015741483</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1581669849073072</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.07336211356916846</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.242354188136892</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1581669849073072</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.08511774496925661</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.7054688639039697</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1581669849073072</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.1946628724357911</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.07772423569579723</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.6591092019327129</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.0121838753886101</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.01568038565429664</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.003442530066615546</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0.05333026154432119</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>-0.008017278091763336</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0.06184335501133797</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.02702424314615259</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.03179268320843731</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.1113481108072819</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.07175592575966946</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.1379031602533945</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.08046307630867644</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.1852776205766054</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.3588877606977632</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.1113481108072819</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.05811494001567974</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1831387853922727</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.1967714297791257</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.01716678696259688</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.02075781813072652</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.1094309685339827</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.117347352252788</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.01645402389252704</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.02127426735957394</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.1612117183471059</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.07981510173169684</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.2437441981554347</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.1612117183471059</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.08119310169084692</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.7190492241917</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.1612117183471059</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1725795383899775</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.09477249613429373</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.5843372205229005</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>-0.01011952165535834</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.01200688273993444</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.02186388726466681</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0.03012020691602513</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>-0.01160507152697798</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0.0422151887277129</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8827,24 +9960,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8875,20 +10006,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -8921,20 +10052,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8970,16 +10105,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -9009,24 +10142,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9057,21 +10188,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9088,37 +10221,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9145,27 +10276,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9192,14 +10321,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -9209,10 +10338,10 @@
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9239,27 +10368,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9286,27 +10415,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9333,27 +10462,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9370,37 +10499,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9417,24 +10546,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -9444,10 +10573,10 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9474,27 +10603,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9521,27 +10650,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9568,27 +10697,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -9615,14 +10744,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -9632,7 +10761,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -9641,6 +10770,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
